--- a/docs/tutorials/files/xslope_liner_bonded.xlsx
+++ b/docs/tutorials/files/xslope_liner_bonded.xlsx
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="F12" s="3">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G12" s="3">
         <v>34.0</v>
@@ -10219,7 +10219,7 @@
         <v>145</v>
       </c>
       <c r="B2" s="3">
-        <v>-5.0</v>
+        <v>-4.0</v>
       </c>
       <c r="D2" s="24" t="s">
         <v>146</v>
@@ -12062,7 +12062,7 @@
         <v>0.0</v>
       </c>
       <c r="B10" s="3">
-        <v>-5.0</v>
+        <v>-4.0</v>
       </c>
       <c r="D10" s="3">
         <v>14.0</v>
@@ -12110,7 +12110,7 @@
         <v>60.0</v>
       </c>
       <c r="B11" s="3">
-        <v>-5.0</v>
+        <v>-4.0</v>
       </c>
       <c r="D11" s="3">
         <v>46.0</v>
@@ -13269,7 +13269,7 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <v>-5.0</v>
+        <v>-4.0</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>

--- a/docs/tutorials/files/xslope_liner_bonded.xlsx
+++ b/docs/tutorials/files/xslope_liner_bonded.xlsx
@@ -13257,20 +13257,10 @@
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="C3" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-      <c r="E3" s="3">
-        <v>-4.0</v>
-      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>

--- a/docs/tutorials/files/xslope_liner_bonded.xlsx
+++ b/docs/tutorials/files/xslope_liner_bonded.xlsx
@@ -3776,11 +3776,11 @@
       </c>
       <c r="H3" s="3" t="str">
         <f>IF($G3="","",IFERROR(VLOOKUP($G3,$AH$8:$AJ$11,2,0),""))</f>
-        <v/>
+        <v>Tangent</v>
       </c>
       <c r="I3" s="3" t="str">
         <f t="shared" ref="I3:I32" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$AH$8:$AJ$11,3,0),""))</f>
-        <v/>
+        <v>Active</v>
       </c>
       <c r="J3" s="3">
         <v>50.0</v>
